--- a/test-cases/TestCases_Futahason.xlsx
+++ b/test-cases/TestCases_Futahason.xlsx
@@ -499,7 +499,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Từ chối SĐT quá ngắn</t>
+          <t xml:space="preserve">Từ chối SĐT bắt đầu bằng 0 nhưng quá ngắn</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -509,7 +509,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Nhập SĐT quá ngắn
+          <t xml:space="preserve">1. Nhập SĐT bắt đầu bằng 0 nhưng quá ngắn
 2. Nhấn "Đăng nhập"</t>
         </is>
       </c>
@@ -520,7 +520,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Không gửi OTP; popup vẫn ở bước nhập SĐT.</t>
+          <t xml:space="preserve">Hiện popup "Số điện thoại không hợp lệ"; không gửi OTP; vẫn ở bước nhập SĐT.</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -803,25 +803,88 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">TC-LOGIN-10</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Đăng nhập</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Từ chối SĐT không bắt đầu bằng 0</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Popup đăng nhập đang mở</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Nhập SĐT đủ độ dài nhưng không bắt đầu bằng 0
+2. Nhấn "Đăng nhập"</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SĐT = "9012345678"</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Không gửi OTP; modal hiện gợi ý "Nhập số điện thoại bắt đầu bằng 0".</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2 - Trung bình</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Negative</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Automated</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">login.spec.ts › TC-LOGIN-10</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tự động ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">TC-SEARCH-01</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Tìm kiếm chuyến xe</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Tìm tuyến hợp lệ trả về chuyến</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ở trang chủ</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Chọn điểm đi: Lào Cai (TP Lào Cai...)
 2. Chọn điểm đến: Hà Nội
@@ -829,223 +892,161 @@
 4. Nhấn "Tìm chuyến"</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Lào Cai → Hà Nội, ngày hôm nay</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Chuyển sang trang /datve/...; hiển thị ≥ 1 chuyến với nút "Chọn chỗ".</t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="H13" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">P1 - Cao</t>
         </is>
       </c>
-      <c r="I12" s="3" t="inlineStr">
+      <c r="I13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Positive</t>
         </is>
       </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Automated</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="inlineStr">
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Automated</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">search-trip.spec.ts › TC-SEARCH-01</t>
         </is>
       </c>
-      <c r="L12" s="3" t="inlineStr">
+      <c r="L13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Tự động ✓</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">TC-SEARCH-02</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Tìm kiếm chuyến xe</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Form phản ánh điểm đi/đến đã chọn</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ở trang chủ</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Chọn điểm đi qua dialog tỉnh → bến
 2. Chọn điểm đến qua dialog tỉnh → bến</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Lào Cai → Hà Nội</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="G14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ô "Chọn điểm đi"/"Chọn điểm đến" hiển thị đúng tên bến đã chọn.</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="H14" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">P2 - Trung bình</t>
         </is>
       </c>
-      <c r="I13" s="3" t="inlineStr">
+      <c r="I14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Positive</t>
         </is>
       </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Automated</t>
-        </is>
-      </c>
-      <c r="K13" s="3" t="inlineStr">
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Automated</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">search-trip.spec.ts › TC-SEARCH-02</t>
         </is>
       </c>
-      <c r="L13" s="3" t="inlineStr">
+      <c r="L14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Tự động ✓</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">TC-SEARCH-03</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Tìm kiếm chuyến xe</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Chọn bến khi tỉnh trùng tên bến (Hà Nội)</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ở trang chủ</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Mở dialog điểm đến
 2. Mở rộng tỉnh "Hà Nội"
 3. Chọn bến con "Hà Nội"</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Điểm đến: Hà Nội</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Chọn đúng bến con (không nhầm với header tỉnh); giá trị ô = "Hà Nội".</t>
         </is>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="H15" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">P2 - Trung bình</t>
         </is>
       </c>
-      <c r="I14" s="3" t="inlineStr">
+      <c r="I15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Positive</t>
         </is>
       </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Automated</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="inlineStr">
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Automated</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">search-trip.spec.ts › TC-SEARCH-01/02</t>
-        </is>
-      </c>
-      <c r="L14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tự động ✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TC-SEARCH-04</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tìm kiếm chuyến xe</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Chặn tìm khi thiếu điểm đi</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ở trang chủ, chưa chọn điểm đi</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Nhấn "Tìm chuyến"</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Điểm đi = (rỗng)</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Hiển thị thông báo "Bạn chưa chọn điểm xuất phát"; không chuyển trang.</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1 - Cao</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Negative</t>
-        </is>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Automated</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">search-trip.spec.ts › TC-SEARCH-04</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
@@ -1057,120 +1058,120 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">TC-SEARCH-04</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tìm kiếm chuyến xe</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chặn tìm khi thiếu điểm đi</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ở trang chủ, chưa chọn điểm đi</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Nhấn "Tìm chuyến"</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Điểm đi = (rỗng)</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hiển thị thông báo "Bạn chưa chọn điểm xuất phát"; không chuyển trang.</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1 - Cao</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Negative</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Automated</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">search-trip.spec.ts › TC-SEARCH-04</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tự động ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">TC-SEARCH-05</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Tìm kiếm chuyến xe</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Chặn tìm khi thiếu điểm đến</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Đã chọn điểm đi, chưa chọn điểm đến</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Chọn điểm đi
 2. Nhấn "Tìm chuyến"</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="F17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Điểm đến = (rỗng)</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="G17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Hiển thị thông báo "Bạn chưa chọn điểm đến"; không chuyển trang.</t>
         </is>
       </c>
-      <c r="H16" s="4" t="inlineStr">
+      <c r="H17" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">P1 - Cao</t>
         </is>
       </c>
-      <c r="I16" s="3" t="inlineStr">
+      <c r="I17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Negative</t>
         </is>
       </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Automated</t>
-        </is>
-      </c>
-      <c r="K16" s="3" t="inlineStr">
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Automated</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">search-trip.spec.ts › TC-SEARCH-05</t>
-        </is>
-      </c>
-      <c r="L16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tự động ✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TC-SEARCH-06</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tìm kiếm chuyến xe</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ngày khởi hành mặc định đúng định dạng</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ở trang chủ</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Quan sát ô "Ngày khởi hành"</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ngày mặc định theo định dạng dd/MM/yyyy (ví dụ 06/06/2026).</t>
-        </is>
-      </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P3 - Thấp</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Positive</t>
-        </is>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Automated</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">search-trip.spec.ts › TC-SEARCH-06</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
@@ -1182,7 +1183,7 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">TC-SEARCH-07</t>
+          <t xml:space="preserve">TC-SEARCH-06</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -1192,32 +1193,32 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thẻ chuyến hiển thị giá và loại xe</t>
+          <t xml:space="preserve">Ngày khởi hành mặc định đúng định dạng</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Đã có kết quả tìm kiếm</t>
+          <t xml:space="preserve">Ở trang chủ</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Quan sát các thẻ chuyến</t>
+          <t xml:space="preserve">1. Quan sát ô "Ngày khởi hành"</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lào Cai → Hà Nội</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mỗi thẻ có giá "Từ ...đ" và loại xe (ECONOMY/VIP/ROYAL CABIN).</t>
+          <t xml:space="preserve">Ngày mặc định theo định dạng dd/MM/yyyy (ví dụ 06/06/2026).</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2 - Trung bình</t>
+          <t xml:space="preserve">P3 - Thấp</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
@@ -1232,7 +1233,7 @@
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">search-trip.spec.ts › TC-SEARCH-07</t>
+          <t xml:space="preserve">search-trip.spec.ts › TC-SEARCH-06</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
@@ -1244,7 +1245,7 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">TC-SEARCH-08</t>
+          <t xml:space="preserve">TC-SEARCH-07</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1254,27 +1255,27 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bật/tắt tùy chọn Khứ hồi</t>
+          <t xml:space="preserve">Thẻ chuyến hiển thị giá và loại xe</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ở trang chủ</t>
+          <t xml:space="preserve">Đã có kết quả tìm kiếm</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Nhấn checkbox "Khứ hồi"</t>
+          <t xml:space="preserve">1. Quan sát các thẻ chuyến</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">Lào Cai → Hà Nội</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Checkbox chuyển sang trạng thái đã chọn (bật ô ngày về).</t>
+          <t xml:space="preserve">Mỗi thẻ có giá "Từ ...đ" và loại xe (ECONOMY/VIP/ROYAL CABIN).</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
@@ -1294,7 +1295,7 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">search-trip.spec.ts › TC-SEARCH-08</t>
+          <t xml:space="preserve">search-trip.spec.ts › TC-SEARCH-07</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
@@ -1306,195 +1307,195 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">TC-SEARCH-08</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tìm kiếm chuyến xe</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bật/tắt tùy chọn Khứ hồi</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ở trang chủ</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Nhấn checkbox "Khứ hồi"</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Checkbox chuyển sang trạng thái đã chọn (bật ô ngày về).</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2 - Trung bình</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Positive</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Automated</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">search-trip.spec.ts › TC-SEARCH-08</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tự động ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">TC-SEARCH-09</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Tìm kiếm chuyến xe</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Tuyến không có chuyến → trạng thái rỗng</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ở trang chủ</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="E21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Chọn tuyến/ngày không có chuyến
 2. Nhấn "Tìm chuyến"</t>
         </is>
       </c>
-      <c r="F20" s="3" t="inlineStr">
+      <c r="F21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Tuyến hiếm / ngày xa</t>
         </is>
       </c>
-      <c r="G20" s="3" t="inlineStr">
+      <c r="G21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Hiển thị thông báo không có chuyến phù hợp (cần xác nhận nội dung thực tế).</t>
         </is>
       </c>
-      <c r="H20" s="4" t="inlineStr">
+      <c r="H21" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">P2 - Trung bình</t>
         </is>
       </c>
-      <c r="I20" s="3" t="inlineStr">
+      <c r="I21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Negative</t>
         </is>
       </c>
-      <c r="J20" s="4" t="inlineStr">
+      <c r="J21" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Manual (cần xác nhận hành vi)</t>
         </is>
       </c>
-      <c r="K20" s="3" t="inlineStr">
+      <c r="K21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="L20" s="3" t="inlineStr">
+      <c r="L21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Thủ công</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">TC-SEARCH-10</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Tìm kiếm chuyến xe</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Không cho chọn ngày trong quá khứ</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ở trang chủ</t>
         </is>
       </c>
-      <c r="E21" s="3" t="inlineStr">
+      <c r="E22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Mở lịch chọn ngày
 2. Thử chọn ngày quá khứ</t>
         </is>
       </c>
-      <c r="F21" s="3" t="inlineStr">
+      <c r="F22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ngày &lt; hôm nay</t>
         </is>
       </c>
-      <c r="G21" s="3" t="inlineStr">
+      <c r="G22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ngày quá khứ bị vô hiệu hóa / không chọn được.</t>
         </is>
       </c>
-      <c r="H21" s="4" t="inlineStr">
+      <c r="H22" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">P3 - Thấp</t>
         </is>
       </c>
-      <c r="I21" s="3" t="inlineStr">
+      <c r="I22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Negative</t>
         </is>
       </c>
-      <c r="J21" s="4" t="inlineStr">
+      <c r="J22" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Manual (date picker)</t>
         </is>
       </c>
-      <c r="K21" s="3" t="inlineStr">
+      <c r="K22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="L21" s="3" t="inlineStr">
+      <c r="L22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Thủ công</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TC-PAY-01</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Điền thông tin thanh toán</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mở sơ đồ chọn ghế</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Đang ở trang kết quả /datve/...</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Nhấn "Chọn chỗ" trên một chuyến</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Chuyến đầu tiên</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mở sơ đồ ghế (Tầng 1/2; ghế C1-1...) kèm chú thích Ghế trống/Đang chọn/Đã đặt.</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1 - Cao</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Positive</t>
-        </is>
-      </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Automated</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">payment-info.spec.ts › TC-PAY-01</t>
-        </is>
-      </c>
-      <c r="L22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tự động ✓</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">TC-PAY-02</t>
+          <t xml:space="preserve">TC-PAY-01</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -1504,27 +1505,27 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chọn một ghế còn trống</t>
+          <t xml:space="preserve">Mở sơ đồ chọn ghế</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sơ đồ ghế đang mở</t>
+          <t xml:space="preserve">Đang ở trang kết quả /datve/...</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Nhấn một ghế còn trống</t>
+          <t xml:space="preserve">1. Nhấn "Chọn chỗ" trên một chuyến</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ghế C1-1</t>
+          <t xml:space="preserve">Chuyến đầu tiên</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ghế chuyển trạng thái "Đang chọn"; cho phép bước tiếp theo.</t>
+          <t xml:space="preserve">Mở sơ đồ ghế (Tầng 1/2; ghế C1-1...) kèm chú thích Ghế trống/Đang chọn/Đã đặt.</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
@@ -1539,12 +1540,12 @@
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Automated (qua luồng)</t>
+          <t xml:space="preserve">Automated</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">payment-info.spec.ts › TC-PAY-03/05/06</t>
+          <t xml:space="preserve">payment-info.spec.ts › TC-PAY-01</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
@@ -1556,7 +1557,7 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">TC-PAY-03</t>
+          <t xml:space="preserve">TC-PAY-02</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1566,27 +1567,27 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bắt buộc đồng ý điều khoản trước khi tiếp tục</t>
+          <t xml:space="preserve">Chọn một ghế còn trống</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Đã chọn ghế, chưa tick điều khoản</t>
+          <t xml:space="preserve">Sơ đồ ghế đang mở</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Nhấn "Tiếp tục" khi chưa tick "Tôi đồng ý với điều khoản"</t>
+          <t xml:space="preserve">1. Nhấn một ghế còn trống</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">Ghế C1-1</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hiển thị thông báo "Bạn chưa đồng ý với điều khoản..."; không qua bước sau.</t>
+          <t xml:space="preserve">Ghế chuyển trạng thái "Đang chọn"; cho phép bước tiếp theo.</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
@@ -1596,17 +1597,17 @@
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Negative</t>
+          <t xml:space="preserve">Positive</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Automated</t>
+          <t xml:space="preserve">Automated (qua luồng)</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">payment-info.spec.ts › TC-PAY-03</t>
+          <t xml:space="preserve">payment-info.spec.ts › TC-PAY-03/05/06</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
@@ -1618,120 +1619,120 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">TC-PAY-03</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Điền thông tin thanh toán</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bắt buộc đồng ý điều khoản trước khi tiếp tục</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Đã chọn ghế, chưa tick điều khoản</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Nhấn "Tiếp tục" khi chưa tick "Tôi đồng ý với điều khoản"</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hiển thị thông báo "Bạn chưa đồng ý với điều khoản..."; không qua bước sau.</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1 - Cao</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Negative</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Automated</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">payment-info.spec.ts › TC-PAY-03</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tự động ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">TC-PAY-04</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Điền thông tin thanh toán</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Đồng ý điều khoản qua popup</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
+      <c r="D26" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Đã chọn ghế</t>
         </is>
       </c>
-      <c r="E25" s="3" t="inlineStr">
+      <c r="E26" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Tick checkbox điều khoản
 2. Đồng ý ở popup điều khoản (nếu mở)</t>
         </is>
       </c>
-      <c r="F25" s="3" t="inlineStr">
+      <c r="F26" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="G25" s="3" t="inlineStr">
+      <c r="G26" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Checkbox điều khoản ở trạng thái đã chọn; cho phép "Tiếp tục".</t>
         </is>
       </c>
-      <c r="H25" s="4" t="inlineStr">
+      <c r="H26" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">P2 - Trung bình</t>
         </is>
       </c>
-      <c r="I25" s="3" t="inlineStr">
+      <c r="I26" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Positive</t>
         </is>
       </c>
-      <c r="J25" s="4" t="inlineStr">
+      <c r="J26" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Automated (qua luồng)</t>
         </is>
       </c>
-      <c r="K25" s="3" t="inlineStr">
+      <c r="K26" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">payment-info.spec.ts › TC-PAY-05/06</t>
-        </is>
-      </c>
-      <c r="L25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tự động ✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TC-PAY-05</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Điền thông tin thanh toán</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bắt buộc chọn điểm đón/trả trước khi xác nhận</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Đã chọn ghế + đồng ý điều khoản + nhấn Tiếp tục</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Nhấn "Xác nhận" khi chưa chọn điểm đón và điểm trả</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Hiển thị thông báo "Bạn vui lòng chọn điểm đón/trả".</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1 - Cao</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Negative</t>
-        </is>
-      </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Automated</t>
-        </is>
-      </c>
-      <c r="K26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">payment-info.spec.ts › TC-PAY-05</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
@@ -1743,7 +1744,7 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">TC-PAY-06</t>
+          <t xml:space="preserve">TC-PAY-05</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -1753,27 +1754,27 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yêu cầu đăng nhập trước khi tới trang thanh toán</t>
+          <t xml:space="preserve">Bắt buộc chọn điểm đón/trả trước khi xác nhận</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Đã chọn ghế + điều khoản + điểm đón + điểm trả</t>
+          <t xml:space="preserve">Đã chọn ghế + đồng ý điều khoản + nhấn Tiếp tục</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Nhấn "Xác nhận"</t>
+          <t xml:space="preserve">1. Nhấn "Xác nhận" khi chưa chọn điểm đón và điểm trả</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Người dùng CHƯA đăng nhập</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hiển thị popup đăng nhập OTP (trang điền thông tin thanh toán bị chặn sau đăng nhập).</t>
+          <t xml:space="preserve">Hiển thị thông báo "Bạn vui lòng chọn điểm đón/trả".</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
@@ -1783,7 +1784,7 @@
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Security/Positive</t>
+          <t xml:space="preserve">Negative</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -1793,7 +1794,7 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">payment-info.spec.ts › TC-PAY-06</t>
+          <t xml:space="preserve">payment-info.spec.ts › TC-PAY-05</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
@@ -1805,7 +1806,7 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">TC-PAY-07</t>
+          <t xml:space="preserve">TC-PAY-06</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1815,59 +1816,59 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Không truy cập trang thanh toán khi chưa đăng nhập (deep-link)</t>
+          <t xml:space="preserve">Yêu cầu đăng nhập trước khi tới trang thanh toán</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chưa đăng nhập</t>
+          <t xml:space="preserve">Đã chọn ghế + điều khoản + điểm đón + điểm trả</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Mở trực tiếp URL bước thanh toán (nếu có)</t>
+          <t xml:space="preserve">1. Nhấn "Xác nhận"</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">URL bước thanh toán</t>
+          <t xml:space="preserve">Người dùng CHƯA đăng nhập</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bị chuyển hướng/yêu cầu đăng nhập, không lộ thông tin thanh toán.</t>
+          <t xml:space="preserve">Hiển thị popup đăng nhập OTP (trang điền thông tin thanh toán bị chặn sau đăng nhập).</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2 - Trung bình</t>
+          <t xml:space="preserve">P1 - Cao</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Security</t>
+          <t xml:space="preserve">Security/Positive</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Manual (cần xác nhận URL)</t>
+          <t xml:space="preserve">Automated</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">payment-info.spec.ts › TC-PAY-06</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thủ công</t>
+          <t xml:space="preserve">Tự động ✓</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">TC-PAY-08</t>
+          <t xml:space="preserve">TC-PAY-07</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -1877,77 +1878,139 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hiển thị form thông tin hành khách/thanh toán (đã đăng nhập)</t>
+          <t xml:space="preserve">Không truy cập trang thanh toán khi chưa đăng nhập (deep-link)</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Đã đăng nhập (auth/user.json) + hoàn tất bước chọn ghế/điểm đón trả</t>
+          <t xml:space="preserve">Chưa đăng nhập</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Nhấn "Xác nhận"</t>
+          <t xml:space="preserve">1. Mở trực tiếp URL bước thanh toán (nếu có)</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Phiên đăng nhập hợp lệ</t>
+          <t xml:space="preserve">URL bước thanh toán</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hiển thị form điền thông tin: Họ tên, SĐT, Email và lựa chọn phương thức thanh toán.</t>
+          <t xml:space="preserve">Bị chuyển hướng/yêu cầu đăng nhập, không lộ thông tin thanh toán.</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1 - Cao</t>
+          <t xml:space="preserve">P2 - Trung bình</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive</t>
+          <t xml:space="preserve">Security</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Partial (cần auth)</t>
+          <t xml:space="preserve">Manual (cần xác nhận URL)</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">payment-info.spec.ts › TC-PAY-08</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chặn: cần tài khoản test</t>
+          <t xml:space="preserve">Thủ công</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">TC-PAY-08</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Điền thông tin thanh toán</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hiển thị form thông tin hành khách/thanh toán (đã đăng nhập)</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Đã đăng nhập (auth/user.json) + hoàn tất bước chọn ghế/điểm đón trả</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Nhấn "Xác nhận"</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Phiên đăng nhập hợp lệ</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hiển thị form điền thông tin: Họ tên, SĐT, Email và lựa chọn phương thức thanh toán.</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1 - Cao</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Positive</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Partial (cần auth)</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">payment-info.spec.ts › TC-PAY-08</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chặn: cần tài khoản test</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">TC-PAY-09</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Điền thông tin thanh toán</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Điền thông tin liên hệ hành khách (không thanh toán)</t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr">
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Đang ở form thông tin thanh toán</t>
         </is>
       </c>
-      <c r="E30" s="3" t="inlineStr">
+      <c r="E31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Nhập Họ tên
 2. Nhập SĐT
@@ -1955,226 +2018,226 @@
 4. KHÔNG nhấn thanh toán</t>
         </is>
       </c>
-      <c r="F30" s="3" t="inlineStr">
+      <c r="F31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Nguyễn Văn Test / 0901234567 / qa@example.com</t>
         </is>
       </c>
-      <c r="G30" s="3" t="inlineStr">
+      <c r="G31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Các trường nhận đúng giá trị; tổng tiền hiển thị đúng (không hoàn tất thanh toán).</t>
         </is>
       </c>
-      <c r="H30" s="4" t="inlineStr">
+      <c r="H31" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">P1 - Cao</t>
         </is>
       </c>
-      <c r="I30" s="3" t="inlineStr">
+      <c r="I31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Positive</t>
         </is>
       </c>
-      <c r="J30" s="4" t="inlineStr">
+      <c r="J31" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Partial (cần auth)</t>
         </is>
       </c>
-      <c r="K30" s="3" t="inlineStr">
+      <c r="K31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">payment-info.spec.ts › TC-PAY-09</t>
         </is>
       </c>
-      <c r="L30" s="3" t="inlineStr">
+      <c r="L31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Chặn: cần tài khoản test</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">TC-PAY-10</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Điền thông tin thanh toán</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="C32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Validate các trường bắt buộc trên form thanh toán</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
+      <c r="D32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Đang ở form thông tin thanh toán</t>
         </is>
       </c>
-      <c r="E31" s="3" t="inlineStr">
+      <c r="E32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Bỏ trống Họ tên/SĐT/Email
 2. Thử tiếp tục/thanh toán</t>
         </is>
       </c>
-      <c r="F31" s="3" t="inlineStr">
+      <c r="F32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Trường bắt buộc rỗng / email sai định dạng</t>
         </is>
       </c>
-      <c r="G31" s="3" t="inlineStr">
+      <c r="G32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Hiển thị lỗi bắt buộc tương ứng; chặn tiếp tục (cần xác nhận selector thực tế).</t>
         </is>
       </c>
-      <c r="H31" s="4" t="inlineStr">
+      <c r="H32" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">P2 - Trung bình</t>
         </is>
       </c>
-      <c r="I31" s="3" t="inlineStr">
+      <c r="I32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Negative</t>
         </is>
       </c>
-      <c r="J31" s="4" t="inlineStr">
+      <c r="J32" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Manual (cần auth + xác nhận form)</t>
         </is>
       </c>
-      <c r="K31" s="3" t="inlineStr">
+      <c r="K32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="L31" s="3" t="inlineStr">
+      <c r="L32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Thủ công</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">TC-PAY-11</t>
         </is>
       </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Điền thông tin thanh toán</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Tổng tiền = giá ghế × số ghế</t>
         </is>
       </c>
-      <c r="D32" s="3" t="inlineStr">
+      <c r="D33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Đang ở form thông tin thanh toán</t>
         </is>
       </c>
-      <c r="E32" s="3" t="inlineStr">
+      <c r="E33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Chọn N ghế
 2. Quan sát tổng tiền</t>
         </is>
       </c>
-      <c r="F32" s="3" t="inlineStr">
+      <c r="F33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ví dụ 2 ghế × 290.000đ</t>
         </is>
       </c>
-      <c r="G32" s="3" t="inlineStr">
+      <c r="G33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Tổng tiền hiển thị đúng = đơn giá × số ghế (+ phụ phí nếu có).</t>
         </is>
       </c>
-      <c r="H32" s="4" t="inlineStr">
+      <c r="H33" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">P2 - Trung bình</t>
         </is>
       </c>
-      <c r="I32" s="3" t="inlineStr">
+      <c r="I33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Positive</t>
         </is>
       </c>
-      <c r="J32" s="4" t="inlineStr">
+      <c r="J33" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Manual (cần auth)</t>
         </is>
       </c>
-      <c r="K32" s="3" t="inlineStr">
+      <c r="K33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="L32" s="3" t="inlineStr">
+      <c r="L33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Thủ công</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">TC-PAY-12</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Điền thông tin thanh toán</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="C34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">CHÍNH SÁCH: không hoàn tất thanh toán thật trên production</t>
         </is>
       </c>
-      <c r="D33" s="3" t="inlineStr">
+      <c r="D34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Mọi test thanh toán</t>
         </is>
       </c>
-      <c r="E33" s="3" t="inlineStr">
+      <c r="E34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Chỉ điền thông tin
 2. KHÔNG bấm nút thanh toán cuối trên môi trường thật</t>
         </is>
       </c>
-      <c r="F33" s="3" t="inlineStr">
+      <c r="F34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ALLOW_REAL_BOOKING=false</t>
         </is>
       </c>
-      <c r="G33" s="3" t="inlineStr">
+      <c r="G34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Bộ test không bao giờ tạo đơn/thanh toán thật trên production. Chỉ chạy đầy đủ trên môi trường staging/sandbox.</t>
         </is>
       </c>
-      <c r="H33" s="4" t="inlineStr">
+      <c r="H34" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">P1 - Cao</t>
         </is>
       </c>
-      <c r="I33" s="3" t="inlineStr">
+      <c r="I34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Policy</t>
         </is>
       </c>
-      <c r="J33" s="4" t="inlineStr">
+      <c r="J34" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Policy</t>
         </is>
       </c>
-      <c r="K33" s="3" t="inlineStr">
+      <c r="K34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">CLAUDE.md › An toàn production</t>
         </is>
       </c>
-      <c r="L33" s="3" t="inlineStr">
+      <c r="L34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Bắt buộc</t>
         </is>
@@ -2250,12 +2313,12 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -2316,12 +2379,12 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">31</t>
+          <t xml:space="preserve">32</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2404,7 +2467,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="C10" s="0" t="inlineStr">
@@ -2702,17 +2765,17 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">TC-SEARCH-01</t>
+          <t xml:space="preserve">TC-LOGIN-10</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tìm kiếm chuyến xe</t>
+          <t xml:space="preserve">Đăng nhập</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">search-trip.spec.ts › TC-SEARCH-01</t>
+          <t xml:space="preserve">login.spec.ts › TC-LOGIN-10</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -2724,7 +2787,7 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">TC-SEARCH-02</t>
+          <t xml:space="preserve">TC-SEARCH-01</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -2734,7 +2797,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">search-trip.spec.ts › TC-SEARCH-02</t>
+          <t xml:space="preserve">search-trip.spec.ts › TC-SEARCH-01</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -2746,7 +2809,7 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">TC-SEARCH-03</t>
+          <t xml:space="preserve">TC-SEARCH-02</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -2756,7 +2819,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">search-trip.spec.ts › TC-SEARCH-01/02</t>
+          <t xml:space="preserve">search-trip.spec.ts › TC-SEARCH-02</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -2768,7 +2831,7 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">TC-SEARCH-04</t>
+          <t xml:space="preserve">TC-SEARCH-03</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -2778,7 +2841,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">search-trip.spec.ts › TC-SEARCH-04</t>
+          <t xml:space="preserve">search-trip.spec.ts › TC-SEARCH-01/02</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -2790,7 +2853,7 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">TC-SEARCH-05</t>
+          <t xml:space="preserve">TC-SEARCH-04</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -2800,7 +2863,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">search-trip.spec.ts › TC-SEARCH-05</t>
+          <t xml:space="preserve">search-trip.spec.ts › TC-SEARCH-04</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -2812,7 +2875,7 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">TC-SEARCH-06</t>
+          <t xml:space="preserve">TC-SEARCH-05</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -2822,7 +2885,7 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">search-trip.spec.ts › TC-SEARCH-06</t>
+          <t xml:space="preserve">search-trip.spec.ts › TC-SEARCH-05</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -2834,7 +2897,7 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">TC-SEARCH-07</t>
+          <t xml:space="preserve">TC-SEARCH-06</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -2844,7 +2907,7 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">search-trip.spec.ts › TC-SEARCH-07</t>
+          <t xml:space="preserve">search-trip.spec.ts › TC-SEARCH-06</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -2856,7 +2919,7 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">TC-SEARCH-08</t>
+          <t xml:space="preserve">TC-SEARCH-07</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2866,7 +2929,7 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">search-trip.spec.ts › TC-SEARCH-08</t>
+          <t xml:space="preserve">search-trip.spec.ts › TC-SEARCH-07</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -2878,7 +2941,7 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">TC-SEARCH-09</t>
+          <t xml:space="preserve">TC-SEARCH-08</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -2888,19 +2951,19 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">search-trip.spec.ts › TC-SEARCH-08</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Manual (cần xác nhận hành vi)</t>
+          <t xml:space="preserve">Automated</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">TC-SEARCH-10</t>
+          <t xml:space="preserve">TC-SEARCH-09</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -2915,36 +2978,36 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Manual (date picker)</t>
+          <t xml:space="preserve">Manual (cần xác nhận hành vi)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">TC-PAY-01</t>
+          <t xml:space="preserve">TC-SEARCH-10</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Điền thông tin thanh toán</t>
+          <t xml:space="preserve">Tìm kiếm chuyến xe</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">payment-info.spec.ts › TC-PAY-01</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Automated</t>
+          <t xml:space="preserve">Manual (date picker)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">TC-PAY-02</t>
+          <t xml:space="preserve">TC-PAY-01</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -2954,19 +3017,19 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">payment-info.spec.ts › TC-PAY-03/05/06</t>
+          <t xml:space="preserve">payment-info.spec.ts › TC-PAY-01</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Automated (qua luồng)</t>
+          <t xml:space="preserve">Automated</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">TC-PAY-03</t>
+          <t xml:space="preserve">TC-PAY-02</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -2976,19 +3039,19 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">payment-info.spec.ts › TC-PAY-03</t>
+          <t xml:space="preserve">payment-info.spec.ts › TC-PAY-03/05/06</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Automated</t>
+          <t xml:space="preserve">Automated (qua luồng)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">TC-PAY-04</t>
+          <t xml:space="preserve">TC-PAY-03</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -2998,19 +3061,19 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">payment-info.spec.ts › TC-PAY-05/06</t>
+          <t xml:space="preserve">payment-info.spec.ts › TC-PAY-03</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Automated (qua luồng)</t>
+          <t xml:space="preserve">Automated</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">TC-PAY-05</t>
+          <t xml:space="preserve">TC-PAY-04</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -3020,19 +3083,19 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">payment-info.spec.ts › TC-PAY-05</t>
+          <t xml:space="preserve">payment-info.spec.ts › TC-PAY-05/06</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Automated</t>
+          <t xml:space="preserve">Automated (qua luồng)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">TC-PAY-06</t>
+          <t xml:space="preserve">TC-PAY-05</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -3042,7 +3105,7 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">payment-info.spec.ts › TC-PAY-06</t>
+          <t xml:space="preserve">payment-info.spec.ts › TC-PAY-05</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -3054,7 +3117,7 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">TC-PAY-07</t>
+          <t xml:space="preserve">TC-PAY-06</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -3064,19 +3127,19 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">payment-info.spec.ts › TC-PAY-06</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Manual (cần xác nhận URL)</t>
+          <t xml:space="preserve">Automated</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">TC-PAY-08</t>
+          <t xml:space="preserve">TC-PAY-07</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -3086,19 +3149,19 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">payment-info.spec.ts › TC-PAY-08</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Partial (cần auth)</t>
+          <t xml:space="preserve">Manual (cần xác nhận URL)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">TC-PAY-09</t>
+          <t xml:space="preserve">TC-PAY-08</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -3108,7 +3171,7 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">payment-info.spec.ts › TC-PAY-09</t>
+          <t xml:space="preserve">payment-info.spec.ts › TC-PAY-08</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -3120,7 +3183,7 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">TC-PAY-10</t>
+          <t xml:space="preserve">TC-PAY-09</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -3130,19 +3193,19 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">payment-info.spec.ts › TC-PAY-09</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Manual (cần auth + xác nhận form)</t>
+          <t xml:space="preserve">Partial (cần auth)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">TC-PAY-11</t>
+          <t xml:space="preserve">TC-PAY-10</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -3157,27 +3220,49 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Manual (cần auth)</t>
+          <t xml:space="preserve">Manual (cần auth + xác nhận form)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">TC-PAY-11</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Điền thông tin thanh toán</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual (cần auth)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">TC-PAY-12</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Điền thông tin thanh toán</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="C34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">CLAUDE.md › An toàn production</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="D34" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Policy</t>
         </is>
